--- a/data_validation_pandas/data/configs/master_data_setup config.xlsx
+++ b/data_validation_pandas/data/configs/master_data_setup config.xlsx
@@ -90,13 +90,13 @@
     <t>NRIC/FIN</t>
   </si>
   <si>
-    <t>(Debtor type; ==; Individual)</t>
+    <t>(`Debtor type`; ==; Individual)</t>
   </si>
   <si>
     <t>UEN</t>
   </si>
   <si>
-    <t>(Debtor type; == ; Company)</t>
+    <t>(`Debtor type`; == ; Company)</t>
   </si>
   <si>
     <t>Effective from</t>
@@ -105,7 +105,7 @@
     <t>date</t>
   </si>
   <si>
-    <t>01/01/1900-31/12/2999</t>
+    <t>01/01/1900-31/12/2099</t>
   </si>
   <si>
     <t>%d/%m/%Y</t>
@@ -114,7 +114,7 @@
     <t>Effective to</t>
   </si>
   <si>
-    <t>(Effective from; &gt;=; Effective to)</t>
+    <t>(`Effective from`; &gt;=; `Effective to`)</t>
   </si>
   <si>
     <t>Bad debt write-off amount</t>
@@ -158,7 +158,7 @@
     <t>datetime</t>
   </si>
   <si>
-    <t>01/01/1900 00:00:00-31/12/2999 23:59:59</t>
+    <t>01/01/1900 00:00:00-31/12/2099 23:59:59</t>
   </si>
   <si>
     <t>%d/%m/%Y %H:%M:%S</t>
@@ -170,7 +170,7 @@
     <t>Modified On</t>
   </si>
   <si>
-    <t>(Created On; &gt;=; Modified On)</t>
+    <t>(`Created On`; &gt;=; `Modified On`)</t>
   </si>
   <si>
     <t>Modified By</t>
@@ -203,7 +203,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,12 +227,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -294,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -335,11 +329,8 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -647,8 +638,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="45.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="53.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="15" width="105.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="9" width="56.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="105.86214285714286" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -662,7 +653,7 @@
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="153.75">
       <c r="A2" s="12" t="s">
         <v>15</v>
       </c>
@@ -676,7 +667,7 @@
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="14"/>
+      <c r="C3" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -700,11 +691,11 @@
     <col min="7" max="7" style="9" width="16.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="9" width="36.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="9" width="39.57642857142857" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="9" width="21.005" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="9" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="9" width="18.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="9" width="28.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="9" width="20.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="9" width="33.71928571428572" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="9" width="9.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="9" width="45.14785714285715" customWidth="1" bestFit="1"/>
   </cols>
@@ -1225,7 +1216,7 @@
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.25">
       <c r="A16" s="8" t="s">
         <v>51</v>
       </c>
